--- a/budget-transfer/reference/15-decision-log.xlsx
+++ b/budget-transfer/reference/15-decision-log.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="H8" s="32" t="inlineStr">
         <is>
-          <t>予定時期まで移管対象部門に残し、予定時期に期中の稟議で移す（決定事項 No.27）。のちに個別移管を廃止し、全額を一括で移すことにした（決定事項 No.54）</t>
+          <t>予定時期まで移管対象部門に残し、予定時期に期中の稟議で移す（決定事項 No.27）。のちに個別移管を廃止し、全額を一括で移すことにした（決定事項 No.51）</t>
         </is>
       </c>
       <c r="I8" s="46" t="n">
@@ -4734,7 +4734,11 @@
       </c>
       <c r="F8" s="32" t="n"/>
       <c r="G8" s="46" t="n"/>
-      <c r="H8" s="32" t="n"/>
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>（決定事項 No.51 で見直し：個別移管を廃止した）</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="32" t="n">
@@ -4758,7 +4762,11 @@
       </c>
       <c r="F9" s="32" t="n"/>
       <c r="G9" s="46" t="n"/>
-      <c r="H9" s="32" t="n"/>
+      <c r="H9" s="32" t="inlineStr">
+        <is>
+          <t>（確認依頼 No.36・決定事項 No.51 で見直し：移管ステータスは5つになった）</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="18">
       <c r="A10" s="32" t="n">
@@ -4810,7 +4818,11 @@
       </c>
       <c r="F11" s="32" t="n"/>
       <c r="G11" s="46" t="n"/>
-      <c r="H11" s="32" t="n"/>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>（決定事項 No.48 で見直し：経営層への報告は行わない）</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="18">
       <c r="A12" s="32" t="n">
@@ -4906,7 +4918,11 @@
       </c>
       <c r="F15" s="32" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="32" t="n"/>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>（確認依頼 No.37 で見直し：稟議が承認された案件の一覧を渡す）</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="18">
       <c r="A16" s="32" t="n">
@@ -5100,7 +5116,7 @@
       <c r="G23" s="46" t="n"/>
       <c r="H23" s="32" t="inlineStr">
         <is>
-          <t>Runbook 進行役編 §1.5、案件担当編 §1.5</t>
+          <t>Runbook 進行役編 §1.5、案件担当編 §1.5（決定事項 No.41・No.51 で見直し：A-01 と個別移管を廃止した）</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5312,7 @@
       <c r="G30" s="46" t="n"/>
       <c r="H30" s="32" t="inlineStr">
         <is>
-          <t>憲章 第9条第6項、予算移管シート「予算一覧」BA</t>
+          <t>憲章 第9条第6項、予算移管シート「予算一覧」BA（決定事項 No.51 で見直し：保留を廃止し、全額を一括で移す）</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5368,7 @@
       <c r="G32" s="46" t="n"/>
       <c r="H32" s="32" t="inlineStr">
         <is>
-          <t>予算移管シート「業務」、仕様 §3.2、準備完了チェック No.3</t>
+          <t>予算移管シート「業務」、仕様 §3.2、準備完了チェック No.3（確認依頼 No.39 で見直し：W 列は使わず、S・T 列に経過措置の完了予定と手続きの内容を書く）</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5536,7 @@
       <c r="G38" s="46" t="n"/>
       <c r="H38" s="32" t="inlineStr">
         <is>
-          <t>憲章 第10条第2項、Runbook 進行役編 §3.4</t>
+          <t>憲章 第10条第2項、Runbook 進行役編 §3.4（決定事項 No.51 で見直し：保留を廃止した。合意済み・準備完了・対象外のどれか）</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5564,7 @@
       <c r="G39" s="46" t="n"/>
       <c r="H39" s="32" t="inlineStr">
         <is>
-          <t>憲章 第10条、予算移管シート、用語集</t>
+          <t>憲章 第10条、予算移管シート、用語集（決定事項 No.51 で見直し：保留も外し、5つになった）</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="17" min="1" max="1"/>
@@ -6021,6 +6037,27 @@
       </c>
       <c r="E9" s="32" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>確認依頼 No.5・6・8・12・20・27・29・35・36 の反映先に、後の決定で見直したことを注記した。保留課題 No.5 の決定事項の番号を No.51 に直した</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="n"/>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/budget-transfer/reference/15-decision-log.xlsx
+++ b/budget-transfer/reference/15-decision-log.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
     <row r="15" ht="30" customHeight="1" s="18">
       <c r="A15" s="38" t="inlineStr">
         <is>
-          <t>「集計」シートは状態ごとの件数を自動で数える。進捗のまとめ（Runbook 進行役編 §3.7）で保留課題の件数を報告し、TBDの放置を防ぐ。</t>
+          <t>「集計」シートは状態ごとの件数を自動で数える。進捗のまとめ（Runbook 事務局編 §3.7）で保留課題の件数を報告し、TBDの放置を防ぐ。</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
@@ -3441,6 +3441,402 @@
         </is>
       </c>
       <c r="J57" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="32" t="inlineStr">
+        <is>
+          <t>予算移管はプロジェクトではなく、IT部門の各チームが普段の業務として行う活動とし、専用の体制は作らない。文書の中心を IT予算移管ガイドラインとし、方針以外は目安・雛形として、各チームがビジネス部門と合意して決める</t>
+        </is>
+      </c>
+      <c r="F58" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G58" s="32" t="inlineStr">
+        <is>
+          <t>実態に合わせるため（各チームが拠り所とするガイドラインとする）</t>
+        </is>
+      </c>
+      <c r="H58" s="32" t="inlineStr"/>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン、README、全文書</t>
+        </is>
+      </c>
+      <c r="J58" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="32" t="inlineStr">
+        <is>
+          <t>ガイドラインの位置付けを、全社予算策定ガイドライン → IT部門向け予算ガイドライン → 本ガイドラインの順の下位文書とする。上位の定めが優先する</t>
+        </is>
+      </c>
+      <c r="F59" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G59" s="32" t="inlineStr">
+        <is>
+          <t>文書の階層を明らかにするため</t>
+        </is>
+      </c>
+      <c r="H59" s="32" t="inlineStr"/>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン p.2、憲章 第1条</t>
+        </is>
+      </c>
+      <c r="J59" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="32" t="inlineStr">
+        <is>
+          <t>進行役を事務局、案件担当を窓口担当（各チームのメンバーが普段の業務として担う）に改める。キックオフは行わず、活動の開始（ガイドラインの公開と説明）とする。合意の期限・準備完了の確認の期限は目安とする（12月末の移管の稟議の承認は方針）</t>
+        </is>
+      </c>
+      <c r="F60" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G60" s="32" t="inlineStr">
+        <is>
+          <t>プロジェクトではないため</t>
+        </is>
+      </c>
+      <c r="H60" s="32" t="inlineStr"/>
+      <c r="I60" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン、憲章、Runbook、用語集、年間カレンダー、予算移管シート、準備完了チェック</t>
+        </is>
+      </c>
+      <c r="J60" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="32" t="inlineStr">
+        <is>
+          <t>IT関連業務は、部門と SO の両方が R を持って協力する。どちらがどこまでを担うかは案件ごとに協議する</t>
+        </is>
+      </c>
+      <c r="F61" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G61" s="32" t="inlineStr">
+        <is>
+          <t>SO 責任者のフィードバック（部門からの丸投げと IT部門の負担の集中を防ぐ）</t>
+        </is>
+      </c>
+      <c r="H61" s="32" t="inlineStr"/>
+      <c r="I61" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン p.10–11、移管後の役割と業務プロセス §5</t>
+        </is>
+      </c>
+      <c r="J61" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="32" t="inlineStr">
+        <is>
+          <t>経費プロセスに、サービスレベルの要求の決定、利用ルールの決定、契約を続けるかどうかの判断を直接業務として加え、SO の行はモニタリングと見直しの材料の整理に絞る</t>
+        </is>
+      </c>
+      <c r="F62" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G62" s="32" t="inlineStr">
+        <is>
+          <t>SO 責任者のフィードバック（決める行が無かったため）</t>
+        </is>
+      </c>
+      <c r="H62" s="32" t="inlineStr"/>
+      <c r="I62" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン p.11、移管後の役割と業務プロセス §5.2</t>
+        </is>
+      </c>
+      <c r="J62" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="32" t="inlineStr">
+        <is>
+          <t>RACI の適用例（プロジェクト体制・運用体制）を、標準的な役割と成果物の責任の雛形として示す。ベンダーが作る成果物の IT 側は R/C とし、案件ごとに決める</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G63" s="32" t="inlineStr">
+        <is>
+          <t>体制の設計・構築に使えるようにするため</t>
+        </is>
+      </c>
+      <c r="H63" s="32" t="inlineStr"/>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン p.12–13、移管後の役割と業務プロセス §5.0・§5.2</t>
+        </is>
+      </c>
+      <c r="J63" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="32" t="inlineStr">
+        <is>
+          <t>GxP 対象の業務は、品質保証部門が定める SOP・手順が正とする。本書の RACI と齟齬がある場合は品質保証部門の定めに従う</t>
+        </is>
+      </c>
+      <c r="F64" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G64" s="32" t="inlineStr">
+        <is>
+          <t>品質保証部門が公式な権限を持ち、規制準拠を担うため</t>
+        </is>
+      </c>
+      <c r="H64" s="32" t="inlineStr"/>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン p.2・p.16、移管後の役割と業務プロセス §5.2</t>
+        </is>
+      </c>
+      <c r="J64" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="32" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>固定資産は型A（予算を持つ IT部門が資産と償却費も管理する）を標準とし、型B（受益部門が持つ）は事情がある案件で個別に選べる（経理部門の確認を得る）。減価償却費は予算移管の対象ではなく、資産を管理する部門に計上する</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G65" s="32" t="inlineStr">
+        <is>
+          <t>経理部門の見解（外部への説明をシンプルにしたい）。ルール上はどちらも可</t>
+        </is>
+      </c>
+      <c r="H65" s="32" t="inlineStr"/>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン 第3章</t>
+        </is>
+      </c>
+      <c r="J65" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="32" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>IT部門</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>型A では Showback（費用を見せる）と Chargeback（受益部門への計上）を分ける。本社機能は Showback で足り、研究開発・製造に関わる費用と償却費は、会計上の区分を保つため受益部門に配賦する</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>研究開発費・製造原価の区分を保つため（経理部門と確認する）</t>
+        </is>
+      </c>
+      <c r="H66" s="32" t="inlineStr"/>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン 第3章</t>
+        </is>
+      </c>
+      <c r="J66" s="32" t="inlineStr">
         <is>
           <t>予算移管事務局</t>
         </is>
@@ -3464,7 +3860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
@@ -4504,8 +4900,80 @@
         <v>46306</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="18"/>
-    <row r="29" ht="15" customHeight="1" s="18"/>
+    <row r="28" ht="15" customHeight="1" s="18">
+      <c r="A28" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>研究開発・製造に関わる IT 費用と償却費の配賦の方法（研究開発費・試験研究費・製造原価の扱い）</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン 第3章（型A の決める点 ※1）</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>経理部門、予算移管事務局</t>
+        </is>
+      </c>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>研究開発費・製造原価の区分が変わる</t>
+        </is>
+      </c>
+      <c r="G28" s="32" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H28" s="32" t="inlineStr"/>
+      <c r="I28" s="46" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="18">
+      <c r="A29" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>移管の前に取得した資産と、今年度から続く投資案件の資産を IT部門に移すか（型A の決める点 ※2）</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドライン 第3章</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>経理部門、予算移管事務局</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>型A の下で資産の持ち主が二通りになる</t>
+        </is>
+      </c>
+      <c r="G29" s="32" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H29" s="32" t="inlineStr"/>
+      <c r="I29" s="46" t="n"/>
+    </row>
     <row r="30" ht="15" customHeight="1" s="18"/>
     <row r="31" ht="15" customHeight="1" s="18"/>
     <row r="32" ht="15" customHeight="1" s="18"/>
@@ -5857,7 +6325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="17" min="1" max="1"/>
@@ -6058,6 +6526,27 @@
       </c>
       <c r="E10" s="32" t="n"/>
     </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>決定事項 No.55〜No.63（ガイドラインへの再構成、役割の改称、RACI の見直し、GxP、固定資産の型と配賦）と、保留課題 No.25・No.26 を加えた</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="n"/>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
